--- a/data_2nd.xlsx
+++ b/data_2nd.xlsx
@@ -351,321 +351,348 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>X3</t>
+          <t>Coyoacán</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>X4</t>
+          <t>Cuajimalpa de Morelos</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>X5</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>X6</t>
+          <t>Iztacalco</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>X7</t>
+          <t>Iztapalapa</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>X8</t>
+          <t>La Magdalena Contreras</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>X9</t>
+          <t>Milpa Alta</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>X10</t>
+          <t>Álvaro Obregón</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>X11</t>
+          <t>Tláhuac</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>X12</t>
+          <t>Tlalpan</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>X13</t>
+          <t>Xochimilco</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>X14</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>X15</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>X16</t>
+          <t>Miguel Hidalgo</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="B2">
         <v>12</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>8</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
       <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
         <v>14</v>
       </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
         <v>12</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N2">
+        <v>4</v>
+      </c>
+      <c r="O2">
         <v>12</v>
       </c>
-      <c r="O2">
-        <v>3</v>
-      </c>
       <c r="P2">
+        <v>3</v>
+      </c>
+      <c r="Q2">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020-10-04</t>
+        </is>
+      </c>
+      <c r="B3">
         <v>11</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>9</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
       <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
         <v>13</v>
       </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
       <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
         <v>21</v>
       </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P3">
+        <v>4</v>
+      </c>
+      <c r="Q3">
         <v>9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020-10-11</t>
+        </is>
+      </c>
+      <c r="B4">
         <v>8</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>11</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
       <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
         <v>12</v>
       </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
       <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
         <v>14</v>
       </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
       <c r="H4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4">
         <v>8</v>
       </c>
-      <c r="O4">
-        <v>4</v>
-      </c>
       <c r="P4">
+        <v>4</v>
+      </c>
+      <c r="Q4">
         <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>7</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020-10-18</t>
+        </is>
       </c>
       <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
         <v>8</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
       <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
         <v>18</v>
       </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
       <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
         <v>13</v>
       </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>9</v>
       </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
       <c r="K5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>6</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>13</v>
       </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
       <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
         <v>14</v>
       </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -674,752 +701,827 @@
         <v>3</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6">
+        <v>5</v>
+      </c>
+      <c r="Q6">
         <v>7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>9</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
       </c>
       <c r="B7">
         <v>9</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
         <v>14</v>
       </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
       <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
         <v>18</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <v>9</v>
       </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
       <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
         <v>9</v>
       </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
       <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
         <v>8</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>9</v>
       </c>
-      <c r="O7">
-        <v>6</v>
-      </c>
       <c r="P7">
         <v>6</v>
       </c>
+      <c r="Q7">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020-11-08</t>
+        </is>
+      </c>
+      <c r="B8">
         <v>14</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>9</v>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
       <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
         <v>21</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>11</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>20</v>
       </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
       <c r="H8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
         <v>8</v>
       </c>
-      <c r="J8">
-        <v>2</v>
-      </c>
       <c r="K8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P8">
+        <v>5</v>
+      </c>
+      <c r="Q8">
         <v>10</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020-11-15</t>
+        </is>
+      </c>
+      <c r="B9">
         <v>13</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
       <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
         <v>22</v>
       </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
       <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
         <v>19</v>
       </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
       <c r="H9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
         <v>9</v>
       </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9">
+        <v>5</v>
+      </c>
+      <c r="N9">
         <v>8</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>13</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>8</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>12</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020-11-22</t>
+        </is>
       </c>
       <c r="B10">
         <v>12</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
         <v>27</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>11</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>27</v>
       </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
       <c r="H10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M10">
+        <v>4</v>
+      </c>
+      <c r="N10">
         <v>11</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>15</v>
       </c>
-      <c r="O10">
-        <v>7</v>
-      </c>
       <c r="P10">
+        <v>7</v>
+      </c>
+      <c r="Q10">
         <v>17</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2020-11-29</t>
+        </is>
+      </c>
+      <c r="B11">
         <v>19</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>13</v>
       </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
       <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11">
         <v>23</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>14</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>33</v>
       </c>
-      <c r="G11">
-        <v>7</v>
-      </c>
       <c r="H11">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
         <v>11</v>
       </c>
-      <c r="J11">
-        <v>4</v>
-      </c>
       <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="L11">
         <v>9</v>
       </c>
-      <c r="L11">
-        <v>7</v>
-      </c>
       <c r="M11">
+        <v>7</v>
+      </c>
+      <c r="N11">
         <v>9</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>12</v>
       </c>
-      <c r="O11">
-        <v>7</v>
-      </c>
       <c r="P11">
+        <v>7</v>
+      </c>
+      <c r="Q11">
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2020-12-06</t>
+        </is>
+      </c>
+      <c r="B12">
         <v>18</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>29</v>
       </c>
-      <c r="C12">
-        <v>5</v>
-      </c>
       <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
         <v>34</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>18</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>32</v>
       </c>
-      <c r="G12">
-        <v>4</v>
-      </c>
       <c r="H12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
         <v>16</v>
       </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
       <c r="K12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>7</v>
       </c>
       <c r="M12">
+        <v>7</v>
+      </c>
+      <c r="N12">
         <v>12</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>15</v>
       </c>
-      <c r="O12">
-        <v>10</v>
-      </c>
       <c r="P12">
+        <v>10</v>
+      </c>
+      <c r="Q12">
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2020-12-13</t>
+        </is>
+      </c>
+      <c r="B13">
         <v>21</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>22</v>
       </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
       <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
         <v>32</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>13</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>33</v>
       </c>
-      <c r="G13">
-        <v>4</v>
-      </c>
       <c r="H13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
         <v>23</v>
       </c>
-      <c r="J13">
-        <v>5</v>
-      </c>
       <c r="K13">
+        <v>5</v>
+      </c>
+      <c r="L13">
         <v>13</v>
-      </c>
-      <c r="L13">
-        <v>11</v>
       </c>
       <c r="M13">
         <v>11</v>
       </c>
       <c r="N13">
+        <v>11</v>
+      </c>
+      <c r="O13">
         <v>18</v>
       </c>
-      <c r="O13">
-        <v>7</v>
-      </c>
       <c r="P13">
+        <v>7</v>
+      </c>
+      <c r="Q13">
         <v>17</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2020-12-20</t>
+        </is>
+      </c>
+      <c r="B14">
         <v>18</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>22</v>
       </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
       <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
         <v>23</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>14</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>32</v>
       </c>
-      <c r="G14">
-        <v>6</v>
-      </c>
       <c r="H14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
         <v>14</v>
       </c>
-      <c r="J14">
-        <v>5</v>
-      </c>
       <c r="K14">
+        <v>5</v>
+      </c>
+      <c r="L14">
         <v>14</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>12</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>11</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>18</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>9</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>10</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2020-12-27</t>
+        </is>
       </c>
       <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
         <v>21</v>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
       <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
         <v>26</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>17</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>28</v>
       </c>
-      <c r="G15">
-        <v>4</v>
-      </c>
       <c r="H15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
         <v>17</v>
       </c>
-      <c r="J15">
-        <v>5</v>
-      </c>
       <c r="K15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L15">
+        <v>10</v>
+      </c>
+      <c r="M15">
         <v>8</v>
       </c>
-      <c r="M15">
-        <v>10</v>
-      </c>
       <c r="N15">
+        <v>10</v>
+      </c>
+      <c r="O15">
         <v>16</v>
       </c>
-      <c r="O15">
-        <v>6</v>
-      </c>
       <c r="P15">
+        <v>6</v>
+      </c>
+      <c r="Q15">
         <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021-01-03</t>
+        </is>
+      </c>
+      <c r="B16">
         <v>17</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>22</v>
       </c>
-      <c r="C16">
-        <v>5</v>
-      </c>
       <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
         <v>19</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>13</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>27</v>
       </c>
-      <c r="G16">
-        <v>4</v>
-      </c>
       <c r="H16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
         <v>14</v>
       </c>
-      <c r="J16">
-        <v>5</v>
-      </c>
       <c r="K16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M16">
+        <v>7</v>
+      </c>
+      <c r="N16">
         <v>11</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>16</v>
       </c>
-      <c r="O16">
-        <v>7</v>
-      </c>
       <c r="P16">
+        <v>7</v>
+      </c>
+      <c r="Q16">
         <v>14</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021-01-10</t>
+        </is>
+      </c>
+      <c r="B17">
         <v>17</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>18</v>
       </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
       <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17">
         <v>24</v>
       </c>
-      <c r="E17">
-        <v>10</v>
-      </c>
       <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
         <v>27</v>
       </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
       <c r="H17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
         <v>23</v>
       </c>
-      <c r="J17">
-        <v>5</v>
-      </c>
       <c r="K17">
+        <v>5</v>
+      </c>
+      <c r="L17">
         <v>13</v>
       </c>
-      <c r="L17">
-        <v>10</v>
-      </c>
       <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17">
         <v>8</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>16</v>
       </c>
-      <c r="O17">
-        <v>6</v>
-      </c>
       <c r="P17">
+        <v>6</v>
+      </c>
+      <c r="Q17">
         <v>13</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>15</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021-01-17</t>
+        </is>
       </c>
       <c r="B18">
         <v>15</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
         <v>24</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>18</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>34</v>
       </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
       <c r="H18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
         <v>17</v>
       </c>
-      <c r="J18">
-        <v>5</v>
-      </c>
       <c r="K18">
+        <v>5</v>
+      </c>
+      <c r="L18">
         <v>11</v>
       </c>
-      <c r="L18">
-        <v>6</v>
-      </c>
       <c r="M18">
+        <v>6</v>
+      </c>
+      <c r="N18">
         <v>8</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>14</v>
       </c>
-      <c r="O18">
-        <v>6</v>
-      </c>
       <c r="P18">
+        <v>6</v>
+      </c>
+      <c r="Q18">
         <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021-01-24</t>
+        </is>
+      </c>
+      <c r="B19">
         <v>14</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>21</v>
       </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
       <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
         <v>20</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>12</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>33</v>
       </c>
-      <c r="G19">
-        <v>4</v>
-      </c>
       <c r="H19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
         <v>12</v>
       </c>
-      <c r="J19">
-        <v>3</v>
-      </c>
       <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
         <v>12</v>
       </c>
-      <c r="L19">
-        <v>6</v>
-      </c>
       <c r="M19">
+        <v>6</v>
+      </c>
+      <c r="N19">
         <v>8</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>19</v>
       </c>
-      <c r="O19">
-        <v>5</v>
-      </c>
       <c r="P19">
+        <v>5</v>
+      </c>
+      <c r="Q19">
         <v>9</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>11</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2021-01-31</t>
+        </is>
       </c>
       <c r="B20">
         <v>11</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D20">
+        <v>7</v>
+      </c>
+      <c r="E20">
         <v>27</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>12</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>22</v>
       </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
       <c r="H20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
         <v>11</v>
       </c>
-      <c r="J20">
-        <v>2</v>
-      </c>
       <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20">
         <v>8</v>
       </c>
-      <c r="L20">
-        <v>5</v>
-      </c>
       <c r="M20">
+        <v>5</v>
+      </c>
+      <c r="N20">
         <v>11</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>18</v>
       </c>
-      <c r="O20">
-        <v>5</v>
-      </c>
       <c r="P20">
+        <v>5</v>
+      </c>
+      <c r="Q20">
         <v>13</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021-02-07</t>
+        </is>
+      </c>
+      <c r="B21">
         <v>14</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>12</v>
       </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
       <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21">
         <v>22</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>12</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>20</v>
       </c>
-      <c r="G21">
-        <v>3</v>
-      </c>
       <c r="H21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
         <v>13</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>8</v>
       </c>
-      <c r="K21">
-        <v>5</v>
-      </c>
       <c r="L21">
         <v>5</v>
       </c>
@@ -1427,512 +1529,565 @@
         <v>5</v>
       </c>
       <c r="N21">
+        <v>5</v>
+      </c>
+      <c r="O21">
         <v>16</v>
       </c>
-      <c r="O21">
-        <v>4</v>
-      </c>
       <c r="P21">
+        <v>4</v>
+      </c>
+      <c r="Q21">
         <v>8</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>10</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021-02-14</t>
+        </is>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22">
         <v>14</v>
       </c>
-      <c r="E22">
-        <v>10</v>
-      </c>
       <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
         <v>20</v>
       </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N22">
+        <v>7</v>
+      </c>
+      <c r="O22">
         <v>9</v>
       </c>
-      <c r="O22">
-        <v>5</v>
-      </c>
       <c r="P22">
+        <v>5</v>
+      </c>
+      <c r="Q22">
         <v>6</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>5</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021-02-21</t>
+        </is>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
         <v>9</v>
       </c>
-      <c r="E23">
-        <v>7</v>
-      </c>
       <c r="F23">
+        <v>7</v>
+      </c>
+      <c r="G23">
         <v>13</v>
       </c>
-      <c r="G23">
-        <v>3</v>
-      </c>
       <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>10</v>
+      </c>
+      <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23">
+        <v>5</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
+      </c>
+      <c r="N23">
+        <v>7</v>
+      </c>
+      <c r="O23">
+        <v>7</v>
+      </c>
+      <c r="P23">
+        <v>2</v>
+      </c>
+      <c r="Q23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-02-28</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>9</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <v>16</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>13</v>
+      </c>
+      <c r="K24">
+        <v>2</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="M24">
+        <v>3</v>
+      </c>
+      <c r="N24">
+        <v>6</v>
+      </c>
+      <c r="O24">
+        <v>10</v>
+      </c>
+      <c r="P24">
+        <v>4</v>
+      </c>
+      <c r="Q24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2021-03-07</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>11</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
         <v>0</v>
       </c>
-      <c r="I23">
-        <v>10</v>
-      </c>
-      <c r="J23">
-        <v>3</v>
-      </c>
-      <c r="K23">
-        <v>5</v>
-      </c>
-      <c r="L23">
-        <v>3</v>
-      </c>
-      <c r="M23">
-        <v>7</v>
-      </c>
-      <c r="N23">
-        <v>7</v>
-      </c>
-      <c r="O23">
-        <v>2</v>
-      </c>
-      <c r="P23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>4</v>
-      </c>
-      <c r="B24">
-        <v>10</v>
-      </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24">
+      <c r="J25">
+        <v>7</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>3</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
+      <c r="O25">
         <v>9</v>
       </c>
-      <c r="E24">
-        <v>4</v>
-      </c>
-      <c r="F24">
-        <v>16</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-      <c r="H24">
+      <c r="P25">
+        <v>3</v>
+      </c>
+      <c r="Q25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2021-03-14</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>7</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>11</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
         <v>0</v>
       </c>
-      <c r="I24">
-        <v>13</v>
-      </c>
-      <c r="J24">
-        <v>2</v>
-      </c>
-      <c r="K24">
-        <v>3</v>
-      </c>
-      <c r="L24">
-        <v>3</v>
-      </c>
-      <c r="M24">
-        <v>6</v>
-      </c>
-      <c r="N24">
-        <v>10</v>
-      </c>
-      <c r="O24">
-        <v>4</v>
-      </c>
-      <c r="P24">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>3</v>
-      </c>
-      <c r="B25">
-        <v>6</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>10</v>
-      </c>
-      <c r="E25">
-        <v>5</v>
-      </c>
-      <c r="F25">
+      <c r="J26">
+        <v>8</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26">
+        <v>3</v>
+      </c>
+      <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26">
+        <v>6</v>
+      </c>
+      <c r="P26">
+        <v>3</v>
+      </c>
+      <c r="Q26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2021-03-21</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <v>7</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
         <v>11</v>
       </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+      <c r="N27">
+        <v>6</v>
+      </c>
+      <c r="O27">
+        <v>4</v>
+      </c>
+      <c r="P27">
+        <v>3</v>
+      </c>
+      <c r="Q27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2021-03-28</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>5</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>7</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>3</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>6</v>
+      </c>
+      <c r="O28">
+        <v>3</v>
+      </c>
+      <c r="P28">
+        <v>3</v>
+      </c>
+      <c r="Q28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2021-04-04</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
         <v>0</v>
       </c>
-      <c r="I25">
-        <v>7</v>
-      </c>
-      <c r="J25">
-        <v>2</v>
-      </c>
-      <c r="K25">
-        <v>3</v>
-      </c>
-      <c r="L25">
-        <v>2</v>
-      </c>
-      <c r="M25">
-        <v>4</v>
-      </c>
-      <c r="N25">
-        <v>9</v>
-      </c>
-      <c r="O25">
-        <v>3</v>
-      </c>
-      <c r="P25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>4</v>
-      </c>
-      <c r="B26">
-        <v>5</v>
-      </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>7</v>
-      </c>
-      <c r="E26">
-        <v>3</v>
-      </c>
-      <c r="F26">
-        <v>11</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
+      <c r="J29">
+        <v>6</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>2</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>2</v>
+      </c>
+      <c r="O29">
+        <v>4</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
+      </c>
+      <c r="Q29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2021-04-11</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30">
         <v>0</v>
       </c>
-      <c r="I26">
+      <c r="E30">
+        <v>5</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
         <v>8</v>
       </c>
-      <c r="J26">
-        <v>2</v>
-      </c>
-      <c r="K26">
-        <v>3</v>
-      </c>
-      <c r="L26">
-        <v>3</v>
-      </c>
-      <c r="M26">
-        <v>5</v>
-      </c>
-      <c r="N26">
-        <v>6</v>
-      </c>
-      <c r="O26">
-        <v>3</v>
-      </c>
-      <c r="P26">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>5</v>
-      </c>
-      <c r="B27">
-        <v>6</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>10</v>
-      </c>
-      <c r="E27">
-        <v>4</v>
-      </c>
-      <c r="F27">
-        <v>7</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
         <v>0</v>
       </c>
-      <c r="I27">
-        <v>11</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <v>2</v>
-      </c>
-      <c r="M27">
-        <v>6</v>
-      </c>
-      <c r="N27">
-        <v>4</v>
-      </c>
-      <c r="O27">
-        <v>3</v>
-      </c>
-      <c r="P27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>3</v>
-      </c>
-      <c r="B28">
+      <c r="J30">
+        <v>4</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>6</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30">
         <v>8</v>
       </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>5</v>
-      </c>
-      <c r="E28">
-        <v>3</v>
-      </c>
-      <c r="F28">
-        <v>10</v>
-      </c>
-      <c r="G28">
-        <v>2</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>7</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28">
-        <v>3</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <v>6</v>
-      </c>
-      <c r="N28">
-        <v>3</v>
-      </c>
-      <c r="O28">
-        <v>3</v>
-      </c>
-      <c r="P28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>2</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <v>4</v>
-      </c>
-      <c r="F29">
-        <v>8</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>6</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29">
-        <v>2</v>
-      </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
-      <c r="M29">
-        <v>2</v>
-      </c>
-      <c r="N29">
-        <v>4</v>
-      </c>
-      <c r="O29">
-        <v>1</v>
-      </c>
-      <c r="P29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>2</v>
-      </c>
-      <c r="B30">
-        <v>4</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>5</v>
-      </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-      <c r="F30">
-        <v>8</v>
-      </c>
-      <c r="G30">
-        <v>2</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>4</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
-        <v>6</v>
-      </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
-      <c r="M30">
-        <v>3</v>
-      </c>
-      <c r="N30">
-        <v>8</v>
-      </c>
-      <c r="O30">
-        <v>1</v>
-      </c>
       <c r="P30">
+        <v>1</v>
+      </c>
+      <c r="Q30">
         <v>4</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>1</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2021-04-18</t>
+        </is>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
         <v>0</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>9</v>
       </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
       <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
         <v>0</v>
       </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
       <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
         <v>0</v>
       </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
       <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
         <v>0</v>
       </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
       <c r="N31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O31">
+        <v>3</v>
+      </c>
+      <c r="P31">
         <v>0</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>0</v>
       </c>
     </row>
